--- a/data/outputSpecialityRpt/File1/RPT_RPT4025233122954TF_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT4025233122954TF_outputSpecialityRpt.xlsx
@@ -853,17 +853,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -880,48 +880,48 @@
         <v>3</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>3.263119821258325</v>
+        <v>0.1283543016797644</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>3.352002998991467</v>
+        <v>0.04260686221601883</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>3.461725269913146</v>
+        <v>0.03873188334745218</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>3.540439953225071</v>
+        <v>0.03493570552442494</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>3.618467943024178</v>
+        <v>0.03149004512659982</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$8095.773606514468</t>
+          <t>$1027.476236973934</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$8731.336851615146</t>
+          <t>$357.8882225541528</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$9466.321268716974</t>
+          <t>$340.5798952855761</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$10163.41526834504</t>
+          <t>$320.8345140491951</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$10905.620077411018</t>
+          <t>$302.0615298407584</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>58406003204</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1020,98 +1020,98 @@
         <v>3</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>3.270689785432134</v>
+        <v>3.136517305548107</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>3.414630424282703</v>
+        <v>3.199215749149006</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>3.564425520814864</v>
+        <v>3.291623854914739</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>3.712898248811074</v>
+        <v>3.365249839644577</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>3.864910242976473</v>
+        <v>3.438169513775609</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$88102.078125</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$53231.078812151005</t>
+          <t>$95113.78867480152</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$58689.641648875084</t>
+          <t>$99492.33717730765</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$64693.46615682726</t>
+          <t>$104970.65340268423</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$71157.15040582666</t>
+          <t>$110044.44075331693</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$78222.00378075345</t>
+          <t>$115297.68212605864</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$95113.78867480152</t>
         </is>
       </c>
       <c r="V16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$99492.33717730765</t>
         </is>
       </c>
       <c r="W16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$104970.65340268423</t>
         </is>
       </c>
       <c r="X16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$110044.44075331693</t>
         </is>
       </c>
       <c r="Y16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$115297.68212605864</t>
         </is>
       </c>
       <c r="Z16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$21971.939735797638</t>
         </is>
       </c>
       <c r="AA16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$22411.155046961532</t>
         </is>
       </c>
       <c r="AB16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23058.49256599655</t>
         </is>
       </c>
       <c r="AC16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23574.257518611743</t>
         </is>
       </c>
       <c r="AD16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$24085.074622259468</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1160,48 +1160,48 @@
         <v>3</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>0.1283543016797644</v>
+        <v>1.217626465453933</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>0.04260686221601883</v>
+        <v>1.215670185123684</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.03873188334745218</v>
+        <v>1.212574228326744</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.03493570552442494</v>
+        <v>1.20596668031878</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>0.03149004512659983</v>
+        <v>1.198574809183103</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$1027.476236973934</t>
+          <t>$10006.015464766102</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$357.8882225541529</t>
+          <t>$10449.154824197</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$340.579895285576</t>
+          <t>$10902.215591615217</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$320.83451404919504</t>
+          <t>$11362.714835636185</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$302.06152984075834</t>
+          <t>$11835.91154724438</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1312,7 +1312,7 @@
         <v>0.5974401220671471</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>0.5975398073780158</v>
+        <v>0.5975398073780157</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
@@ -1326,22 +1326,22 @@
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>$26035.571265779243</t>
+          <t>$26035.57126577924</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$17913.11346698963</t>
+          <t>$17913.113466989635</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$13032.404402543127</t>
+          <t>$13032.404402543129</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$13133.941904729343</t>
+          <t>$13133.941904729345</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>49702022813</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1437,51 +1437,51 @@
         </is>
       </c>
       <c r="I19" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>3.344926056939333</v>
+        <v>1.710527744988765</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>2.163279690102619</v>
+        <v>1.291723301176847</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>2.155507680301076</v>
+        <v>0.1750644499375648</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>2.248502802516199</v>
+        <v>0.0529844592780824</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>2.372296130820285</v>
+        <v>0.01733876873609616</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$5580.3798828125</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$204692.77041022485</t>
+          <t>$5171.9509904492115</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$135762.23092245896</t>
+          <t>$4138.776961984778</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$138716.28942391867</t>
+          <t>$592.2231114931147</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$148376.2592311176</t>
+          <t>$188.42051721501466</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$160539.67560417514</t>
+          <t>$64.82456869958668</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1583,16 +1583,16 @@
         <v>0</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0.2673947790377587</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1.226837101121379</v>
+        <v>5.005926614509106</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1.206690781946901</v>
+        <v>8.251887082863121</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1.113434018286723</v>
+        <v>9.027015254951646</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
@@ -1606,22 +1606,22 @@
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$771.2095359422179</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$3736.5279108508407</t>
+          <t>$106450.68455427092</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$3864.2491842039617</t>
+          <t>$176832.23828382633</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$3749.051566979945</t>
+          <t>$194938.01147885644</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00069068803</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC IBRANCE</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1708,60 +1708,60 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>1.22076901006598</v>
+        <v>3.344926056939333</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>2.635062791994737</v>
+        <v>2.163279690102619</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>2.955863352140418</v>
+        <v>2.155507680301076</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.139332955797313</v>
+        <v>2.248502802516199</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>3.300019600103826</v>
+        <v>2.372296130820284</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$67240.06568895874</t>
+          <t>$204692.77041022485</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$148858.6925393523</t>
+          <t>$135762.23092245893</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$171260.09591304997</t>
+          <t>$138716.2894239187</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$186551.09710359777</t>
+          <t>$148376.25923111764</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$201124.76331679616</t>
+          <t>$160539.67560417517</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1857,51 +1857,51 @@
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>12.6043459753352</v>
+        <v>3.263119821258325</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>13.32740217929365</v>
+        <v>3.352002998991467</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>9.100856872321929</v>
+        <v>3.461725269913146</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>6.571841342738619</v>
+        <v>3.540439953225071</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>6.572937881158174</v>
+        <v>3.618467943024177</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$293235.9883084476</t>
+          <t>$8095.773606514468</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$312426.8551893509</t>
+          <t>$8731.336851615144</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$214957.3616038756</t>
+          <t>$9466.321268716976</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$156388.85283051748</t>
+          <t>$10163.415268345043</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$157607.30285675213</t>
+          <t>$10905.62007741102</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>0</v>
+        <v>3.270689785432134</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>0</v>
+        <v>3.414630424282703</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.4550842376826458</v>
+        <v>3.564425520814864</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.7501715529875564</v>
+        <v>3.712898248811074</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>0.8206377504501494</v>
+        <v>3.864910242976473</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$53231.078812151005</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$58689.64164887507</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$8870.89037952258</t>
+          <t>$64693.46615682727</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$14736.019856985533</t>
+          <t>$71157.15040582667</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$16244.834289904704</t>
+          <t>$78222.00378075347</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,75 +2113,75 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I24" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1.217626465453933</v>
+        <v>2.402595122825411</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1.215670185123684</v>
+        <v>2.262179095563523</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>1.212574228326744</v>
+        <v>2.060556823882584</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>1.20596668031878</v>
+        <v>1.853753881321507</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>1.198574809183104</v>
+        <v>1.664790201106821</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$10006.015464766102</t>
+          <t>$17310.937970341267</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$10449.154824197001</t>
+          <t>$17104.55494124535</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$10902.215591615213</t>
+          <t>$16312.81569002672</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$11362.714835636183</t>
+          <t>$15330.385669803642</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$11835.911547244377</t>
+          <t>$14381.930699371356</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,75 +2253,75 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>0</v>
+        <v>1.087706607086108</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>0</v>
+        <v>1.117334332997156</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>5.005926614509105</v>
+        <v>1.153908423304382</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>8.251887082863121</v>
+        <v>1.180146651075024</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>9.027015254951644</v>
+        <v>1.206155981008059</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2677.439211535461</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2946.0045177576903</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$106450.68455427095</t>
+          <t>$3250.8061156854587</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$176832.23828382636</t>
+          <t>$3544.8399099043395</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$194938.01147885644</t>
+          <t>$3863.264531558746</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2420,19 +2420,19 @@
         <v>0</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>1.757656948345875</v>
+        <v>0</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>1.748441604247599</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>1.747480134587764</v>
+        <v>0.455084237682646</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>1.733427959659759</v>
+        <v>0.7501715529875564</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>1.716482211696096</v>
+        <v>0.8206377504501495</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
@@ -2441,27 +2441,27 @@
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$13000.494050692918</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$13527.996090287435</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$14145.314932056883</t>
+          <t>$8870.890379522578</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$14707.607785162903</t>
+          <t>$14736.01985698553</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$15265.513526288303</t>
+          <t>$16244.834289904704</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
@@ -2533,75 +2533,75 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>2.402595122825411</v>
+        <v>12.6043459753352</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>2.262179095563523</v>
+        <v>13.32740217929365</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>2.060556823882583</v>
+        <v>9.100856872321929</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>1.853753881321507</v>
+        <v>6.571841342738619</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1.664790201106821</v>
+        <v>6.572937881158173</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$17310.937970341267</t>
+          <t>$293235.9883084476</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>$17104.55494124535</t>
+          <t>$312426.85518935084</t>
         </is>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$16312.815690026724</t>
+          <t>$214957.36160387564</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$15330.385669803645</t>
+          <t>$156388.85283051754</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$14381.930699371356</t>
+          <t>$157607.30285675218</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,75 +2673,75 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>1.087706607086108</v>
+        <v>1.757656948345875</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>1.117334332997156</v>
+        <v>1.748441604247599</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>1.153908423304382</v>
+        <v>1.747480134587764</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>1.180146651075024</v>
+        <v>1.733427959659759</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>1.206155981008059</v>
+        <v>1.716482211696096</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$2677.439211535461</t>
+          <t>$13000.494050692916</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$2946.0045177576912</t>
+          <t>$13527.996090287435</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$3250.806115685458</t>
+          <t>$14145.31493205688</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$3544.8399099043386</t>
+          <t>$14707.6077851629</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$3863.264531558745</t>
+          <t>$15265.513526288303</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2813,125 +2813,125 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>58406003204</t>
+          <t>NEWGENERICS00069068803</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>3.136517305548107</v>
+        <v>1.22076901006598</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>3.199215749149006</v>
+        <v>2.635062791994737</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>3.291623854914739</v>
+        <v>2.955863352140419</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>3.365249839644577</v>
+        <v>3.139332955797313</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>3.43816951377561</v>
+        <v>3.300019600103827</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$88102.078125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$95113.78867480152</t>
+          <t>$67240.06568895873</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$99492.33717730768</t>
+          <t>$148858.6925393523</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$104970.65340268421</t>
+          <t>$171260.09591304994</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$110044.4407533169</t>
+          <t>$186551.0971035977</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$115297.68212605861</t>
+          <t>$201124.76331679616</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
         <is>
-          <t>$95113.78867480152</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V29" s="14" t="inlineStr">
         <is>
-          <t>$99492.33717730768</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W29" s="14" t="inlineStr">
         <is>
-          <t>$104970.65340268421</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X29" s="14" t="inlineStr">
         <is>
-          <t>$110044.4407533169</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y29" s="14" t="inlineStr">
         <is>
-          <t>$115297.68212605861</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z29" s="14" t="inlineStr">
         <is>
-          <t>$21971.939735797638</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA29" s="14" t="inlineStr">
         <is>
-          <t>$22411.155046961532</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB29" s="14" t="inlineStr">
         <is>
-          <t>$23058.49256599655</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC29" s="14" t="inlineStr">
         <is>
-          <t>$23574.257518611743</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD29" s="14" t="inlineStr">
         <is>
-          <t>$24085.074622259475</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>49702022813</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>TIVICAY</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2968,60 +2968,60 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.710527744988765</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1.291723301176847</v>
+        <v>0.2673947790377587</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>0.1750644499375648</v>
+        <v>1.22683710112138</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>0.0529844592780824</v>
+        <v>1.206690781946901</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>0.01733876873609616</v>
+        <v>1.113434018286723</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>$5580.3798828125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$5171.9509904492115</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$4138.776961984779</t>
+          <t>$771.2095359422179</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$592.2231114931146</t>
+          <t>$3736.52791085084</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$188.42051721501463</t>
+          <t>$3864.249184203961</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$64.82456869958666</t>
+          <t>$3749.051566979945</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
